--- a/artfynd/A 11465-2025 artfynd.xlsx
+++ b/artfynd/A 11465-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>94616291</v>
       </c>
       <c r="B2" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>109406809</v>
       </c>
       <c r="B3" t="n">
-        <v>57963</v>
+        <v>57969</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 11465-2025 artfynd.xlsx
+++ b/artfynd/A 11465-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>94616291</v>
       </c>
       <c r="B2" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>109406809</v>
       </c>
       <c r="B3" t="n">
-        <v>57969</v>
+        <v>57972</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 11465-2025 artfynd.xlsx
+++ b/artfynd/A 11465-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>94616291</v>
       </c>
       <c r="B2" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>109406809</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>57973</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
